--- a/benchmarking/evaluation_results/excel/triple_classification.xlsx
+++ b/benchmarking/evaluation_results/excel/triple_classification.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="0.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="0.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="0.1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="0.2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="0.3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.64168</v>
+        <v>0.29417</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6458199999999999</v>
+        <v>0.41419</v>
       </c>
       <c r="D2" t="n">
-        <v>0.64398</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.67077</v>
+        <v>0.44086</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.52581</v>
       </c>
       <c r="F2" t="n">
-        <v>0.53454</v>
+        <v>0.32601</v>
       </c>
       <c r="G2" t="n">
-        <v>0.65433</v>
+        <v>0.23853</v>
       </c>
       <c r="H2" t="n">
-        <v>0.72905</v>
+        <v>0.48109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.64122</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.76239</v>
+        <v>0.24658</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.49431</v>
       </c>
     </row>
     <row r="3">
@@ -520,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.63829</v>
+        <v>0.25314</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64261</v>
+        <v>0.41409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6408700000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.66937</v>
+        <v>0.44077</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.5218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.48492</v>
+        <v>0.30508</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6519200000000001</v>
+        <v>0.23705</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72904</v>
+        <v>0.47876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6379899999999999</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.76217</v>
+        <v>0.24033</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4892</v>
       </c>
     </row>
     <row r="4">
@@ -554,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6733</v>
+        <v>0.07808</v>
       </c>
       <c r="C4" t="n">
-        <v>0.67647</v>
+        <v>0.40661</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67431</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.69085</v>
+        <v>0.43376</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.56556</v>
       </c>
       <c r="F4" t="n">
-        <v>0.64479</v>
+        <v>0.18445</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68089</v>
+        <v>0.20346</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7309099999999999</v>
+        <v>0.51358</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6722</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.75507</v>
+        <v>0.17143</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.54029</v>
       </c>
     </row>
     <row r="5">
@@ -588,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.60328</v>
+        <v>0.4282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.60876</v>
+        <v>0.42157</v>
       </c>
       <c r="D5" t="n">
-        <v>0.60743</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6479</v>
+        <v>0.44777</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.47805</v>
       </c>
       <c r="F5" t="n">
-        <v>0.32505</v>
+        <v>0.4257</v>
       </c>
       <c r="G5" t="n">
-        <v>0.62295</v>
+        <v>0.27065</v>
       </c>
       <c r="H5" t="n">
-        <v>0.72717</v>
+        <v>0.44395</v>
       </c>
       <c r="I5" t="n">
-        <v>0.60378</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.76928</v>
+        <v>0.30923</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.43811</v>
       </c>
     </row>
     <row r="6">
@@ -622,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.64232</v>
+        <v>0.24859</v>
       </c>
       <c r="C6" t="n">
-        <v>0.64688</v>
+        <v>0.43333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.64538</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.67864</v>
+        <v>0.46139</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.5275</v>
       </c>
       <c r="F6" t="n">
-        <v>0.49086</v>
+        <v>0.32974</v>
       </c>
       <c r="G6" t="n">
-        <v>0.65785</v>
+        <v>0.24628</v>
       </c>
       <c r="H6" t="n">
-        <v>0.75654</v>
+        <v>0.48767</v>
       </c>
       <c r="I6" t="n">
-        <v>0.64233</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0.80919</v>
+        <v>0.24806</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4943</v>
       </c>
     </row>
     <row r="7">
@@ -656,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.64824</v>
+        <v>0.35523</v>
       </c>
       <c r="C7" t="n">
-        <v>0.65298</v>
+        <v>0.43408</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6514</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.68516</v>
+        <v>0.46182</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.52864</v>
       </c>
       <c r="F7" t="n">
-        <v>0.49217</v>
+        <v>0.37573</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6642400000000001</v>
+        <v>0.25763</v>
       </c>
       <c r="H7" t="n">
-        <v>0.75796</v>
+        <v>0.48721</v>
       </c>
       <c r="I7" t="n">
-        <v>0.64824</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.80035</v>
+        <v>0.27573</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.49406</v>
       </c>
     </row>
     <row r="8">
@@ -690,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.25</v>
+        <v>-33.95</v>
       </c>
       <c r="C8" t="n">
-        <v>43.02</v>
+        <v>-12.1</v>
       </c>
       <c r="D8" t="n">
-        <v>41.59</v>
-      </c>
-      <c r="E8" t="n">
-        <v>46.55</v>
+        <v>2.64</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>9.859999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>3.14</v>
+        <v>-27.39</v>
       </c>
       <c r="G8" t="n">
-        <v>50.71</v>
+        <v>-39.29</v>
       </c>
       <c r="H8" t="n">
-        <v>64.47</v>
+        <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>33.31</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>78.06</v>
+        <v>-48.64</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -723,32 +724,42 @@
           <t>norm_distance</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.24827</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.22637</v>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>0.16373</v>
+        <v>0.00322</v>
       </c>
       <c r="E9" t="n">
-        <v>0.16338</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01255</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.30764</v>
+        <v>0.01313</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="H9" t="n">
-        <v>0.13304</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.25392</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0.36174</v>
+        <v>0.00088</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.00175</v>
       </c>
     </row>
   </sheetData>
@@ -819,31 +830,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.62065</v>
+        <v>0.64168</v>
       </c>
       <c r="C2" t="n">
-        <v>0.62088</v>
+        <v>0.6458199999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.62007</v>
+        <v>0.64398</v>
       </c>
       <c r="E2" t="n">
-        <v>0.63685</v>
+        <v>0.67077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.61927</v>
+        <v>0.53454</v>
       </c>
       <c r="G2" t="n">
-        <v>0.65778</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.6861699999999999</v>
+        <v>0.65433</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.72905</v>
       </c>
       <c r="I2" t="n">
-        <v>0.61961</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6842200000000001</v>
+        <v>0.64122</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.76239</v>
       </c>
     </row>
     <row r="3">
@@ -853,31 +864,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.61964</v>
+        <v>0.63829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.61983</v>
+        <v>0.64261</v>
       </c>
       <c r="D3" t="n">
-        <v>0.61918</v>
+        <v>0.6408700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.63651</v>
+        <v>0.66937</v>
       </c>
       <c r="F3" t="n">
-        <v>0.61837</v>
+        <v>0.48492</v>
       </c>
       <c r="G3" t="n">
-        <v>0.65772</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.68611</v>
+        <v>0.6519200000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.72904</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6187</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.68381</v>
+        <v>0.6379899999999999</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.76217</v>
       </c>
     </row>
     <row r="4">
@@ -887,31 +898,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.63919</v>
+        <v>0.6733</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6398</v>
+        <v>0.67647</v>
       </c>
       <c r="D4" t="n">
-        <v>0.63757</v>
+        <v>0.67431</v>
       </c>
       <c r="E4" t="n">
-        <v>0.64763</v>
+        <v>0.69085</v>
       </c>
       <c r="F4" t="n">
-        <v>0.63684</v>
+        <v>0.64479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.66213</v>
+        <v>0.68089</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6816</v>
+        <v>0.7309099999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.63737</v>
+        <v>0.6722</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.69515</v>
+        <v>0.75507</v>
       </c>
     </row>
     <row r="5">
@@ -921,31 +932,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6001</v>
+        <v>0.60328</v>
       </c>
       <c r="C5" t="n">
-        <v>0.59985</v>
+        <v>0.60876</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6008</v>
+        <v>0.60743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6254</v>
+        <v>0.6479</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5999</v>
+        <v>0.32505</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6533099999999999</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.69062</v>
+        <v>0.62295</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.72717</v>
       </c>
       <c r="I5" t="n">
-        <v>0.60002</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.67247</v>
+        <v>0.60378</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.76928</v>
       </c>
     </row>
     <row r="6">
@@ -955,31 +966,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.64232</v>
       </c>
       <c r="C6" t="n">
-        <v>0.63154</v>
+        <v>0.64688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.63181</v>
+        <v>0.64538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.65368</v>
+        <v>0.67864</v>
       </c>
       <c r="F6" t="n">
-        <v>0.63097</v>
+        <v>0.49086</v>
       </c>
       <c r="G6" t="n">
-        <v>0.68066</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.72056</v>
+        <v>0.65785</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.75654</v>
       </c>
       <c r="I6" t="n">
-        <v>0.63117</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7003200000000001</v>
+        <v>0.64233</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.80919</v>
       </c>
     </row>
     <row r="7">
@@ -989,31 +1000,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.63578</v>
+        <v>0.64824</v>
       </c>
       <c r="C7" t="n">
-        <v>0.63578</v>
+        <v>0.65298</v>
       </c>
       <c r="D7" t="n">
-        <v>0.63583</v>
+        <v>0.6514</v>
       </c>
       <c r="E7" t="n">
-        <v>0.657</v>
+        <v>0.68516</v>
       </c>
       <c r="F7" t="n">
-        <v>0.63497</v>
+        <v>0.49217</v>
       </c>
       <c r="G7" t="n">
-        <v>0.68248</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.71773</v>
+        <v>0.6642400000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.75796</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6352100000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.70523</v>
+        <v>0.64824</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.80035</v>
       </c>
     </row>
     <row r="8">
@@ -1023,31 +1034,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.95</v>
+        <v>28.25</v>
       </c>
       <c r="C8" t="n">
-        <v>29.51</v>
+        <v>43.02</v>
       </c>
       <c r="D8" t="n">
-        <v>41.23</v>
+        <v>41.59</v>
       </c>
       <c r="E8" t="n">
-        <v>39.68</v>
+        <v>46.55</v>
       </c>
       <c r="F8" t="n">
-        <v>28.24</v>
+        <v>3.14</v>
       </c>
       <c r="G8" t="n">
-        <v>49.5</v>
+        <v>50.71</v>
       </c>
       <c r="H8" t="n">
-        <v>53.44</v>
+        <v>64.47</v>
       </c>
       <c r="I8" t="n">
-        <v>32.55</v>
+        <v>33.31</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>53.48</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="9">
@@ -1057,31 +1068,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.18399</v>
+        <v>0.24827</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1823</v>
+        <v>0.22637</v>
       </c>
       <c r="D9" t="n">
-        <v>0.17611</v>
+        <v>0.16373</v>
       </c>
       <c r="E9" t="n">
-        <v>0.16239</v>
+        <v>0.16338</v>
       </c>
       <c r="F9" t="n">
-        <v>0.12321</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.281</v>
+        <v>0.01255</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.30764</v>
       </c>
       <c r="H9" t="n">
-        <v>0.12976</v>
+        <v>0.13304</v>
       </c>
       <c r="I9" t="n">
-        <v>0.22922</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.19441</v>
+        <v>0.25392</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.36174</v>
       </c>
     </row>
   </sheetData>
@@ -1152,31 +1163,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.58972</v>
+        <v>0.62065</v>
       </c>
       <c r="C2" t="n">
-        <v>0.588</v>
+        <v>0.62088</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5834</v>
+        <v>0.62007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.59398</v>
+        <v>0.63685</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5890300000000001</v>
+        <v>0.61927</v>
       </c>
       <c r="G2" t="n">
-        <v>0.60386</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.6257</v>
+        <v>0.65778</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.6861699999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.58673</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.64789</v>
+        <v>0.61961</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6842200000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1186,31 +1197,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.58971</v>
+        <v>0.61964</v>
       </c>
       <c r="C3" t="n">
-        <v>0.58799</v>
+        <v>0.61983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5834</v>
+        <v>0.61918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.59391</v>
+        <v>0.63651</v>
       </c>
       <c r="F3" t="n">
-        <v>0.58901</v>
+        <v>0.61837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.60368</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.62519</v>
+        <v>0.65772</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.68611</v>
       </c>
       <c r="I3" t="n">
-        <v>0.58673</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.64753</v>
+        <v>0.6187</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.68381</v>
       </c>
     </row>
     <row r="4">
@@ -1220,31 +1231,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.58706</v>
+        <v>0.63919</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5857599999999999</v>
+        <v>0.6398</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5835399999999999</v>
+        <v>0.63757</v>
       </c>
       <c r="E4" t="n">
-        <v>0.58854</v>
+        <v>0.64763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5856</v>
+        <v>0.63684</v>
       </c>
       <c r="G4" t="n">
-        <v>0.59506</v>
+        <v>0.66213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.61127</v>
+        <v>0.6816</v>
       </c>
       <c r="I4" t="n">
-        <v>0.58626</v>
+        <v>0.63737</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.65887</v>
+        <v>0.69515</v>
       </c>
     </row>
     <row r="5">
@@ -1254,31 +1265,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.59235</v>
+        <v>0.6001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.59021</v>
+        <v>0.59985</v>
       </c>
       <c r="D5" t="n">
-        <v>0.58326</v>
+        <v>0.6008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.59927</v>
+        <v>0.6254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.59241</v>
+        <v>0.5999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.61229</v>
+        <v>0.6533099999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6391</v>
+        <v>0.69062</v>
       </c>
       <c r="I5" t="n">
-        <v>0.58721</v>
+        <v>0.60002</v>
       </c>
       <c r="J5" t="n">
-        <v>0.63618</v>
+        <v>0.67247</v>
       </c>
     </row>
     <row r="6">
@@ -1288,31 +1299,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.61626</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.61413</v>
+        <v>0.63154</v>
       </c>
       <c r="D6" t="n">
-        <v>0.60758</v>
+        <v>0.63181</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6229</v>
+        <v>0.65368</v>
       </c>
       <c r="F6" t="n">
-        <v>0.61611</v>
+        <v>0.63097</v>
       </c>
       <c r="G6" t="n">
-        <v>0.63626</v>
+        <v>0.68066</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.66555</v>
+        <v>0.72056</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6115</v>
+        <v>0.63117</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6644600000000001</v>
+        <v>0.7003200000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1322,31 +1333,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.61561</v>
+        <v>0.63578</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6136</v>
+        <v>0.63578</v>
       </c>
       <c r="D7" t="n">
-        <v>0.60761</v>
+        <v>0.63583</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6214499999999999</v>
+        <v>0.657</v>
       </c>
       <c r="F7" t="n">
-        <v>0.61528</v>
+        <v>0.63497</v>
       </c>
       <c r="G7" t="n">
-        <v>0.63352</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.65948</v>
+        <v>0.68248</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.71773</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6114000000000001</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.66816</v>
+        <v>0.6352100000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.70523</v>
       </c>
     </row>
     <row r="8">
@@ -1356,31 +1367,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.13</v>
+        <v>30.95</v>
       </c>
       <c r="C8" t="n">
-        <v>27.07</v>
+        <v>29.51</v>
       </c>
       <c r="D8" t="n">
-        <v>23.78</v>
+        <v>41.23</v>
       </c>
       <c r="E8" t="n">
-        <v>31.92</v>
+        <v>39.68</v>
       </c>
       <c r="F8" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>44.59</v>
+        <v>28.24</v>
+      </c>
+      <c r="G8" t="n">
+        <v>49.5</v>
       </c>
       <c r="H8" t="n">
-        <v>41.81</v>
+        <v>53.44</v>
       </c>
       <c r="I8" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="J8" t="n">
-        <v>42.43</v>
+        <v>32.55</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>53.48</v>
       </c>
     </row>
     <row r="9">
@@ -1390,31 +1401,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.16874</v>
+        <v>0.18399</v>
       </c>
       <c r="C9" t="n">
-        <v>0.14207</v>
+        <v>0.1823</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09932000000000001</v>
+        <v>0.17611</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12539</v>
+        <v>0.16239</v>
       </c>
       <c r="F9" t="n">
-        <v>0.10021</v>
+        <v>0.12321</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.26022</v>
+        <v>0.281</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0906</v>
+        <v>0.12976</v>
       </c>
       <c r="I9" t="n">
-        <v>0.13661</v>
+        <v>0.22922</v>
       </c>
       <c r="J9" t="n">
-        <v>0.16492</v>
+        <v>0.19441</v>
       </c>
     </row>
   </sheetData>
@@ -1485,6 +1496,339 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.58972</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.59398</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5890300000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.60386</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.58673</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.64789</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>f1_macro</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.58971</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.58799</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.59391</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.58901</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.60368</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.62519</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.58673</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.64753</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>f1_pos</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.58706</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5857599999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5835399999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.58854</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5856</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.59506</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.61127</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.58626</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.65887</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f1_neg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.59235</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.59021</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.58326</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.59927</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.59241</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.61229</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.6391</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.58721</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.63618</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.61626</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.61413</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.60758</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.61611</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.63626</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.66555</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6644600000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.61561</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.60761</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6214499999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.61528</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.63352</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.65948</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6114000000000001</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.66816</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Z_statistic</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="I8" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>norm_distance</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.16874</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.09932000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.12539</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.10021</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.13661</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.16492</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TransE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DistMult</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ComplEx</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>HolE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ConvE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PairRE</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AutoSF</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BoxE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RotatE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.53293</v>
       </c>
       <c r="C2" t="n">
